--- a/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92535327247</v>
+        <v>46157.93108399596</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93108399596</v>
+        <v>46157.93364621632</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93364621632</v>
+        <v>46157.93665350573</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93665350573</v>
+        <v>46158.28191086147</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28191086147</v>
+        <v>46158.29709169175</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29709169175</v>
+        <v>46158.29785607146</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29785607146</v>
+        <v>46158.33352297456</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33352297456</v>
+        <v>46158.37208764383</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.2_Ходатайства/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37208764383</v>
+        <v>46158.3742494302</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
